--- a/outputs/Block2_Popular_Vote_Validation_v12.xlsx
+++ b/outputs/Block2_Popular_Vote_Validation_v12.xlsx
@@ -979,7 +979,7 @@
         <v>44.9</v>
       </c>
       <c r="D13">
-        <v>47.73119999999993</v>
+        <v>47.73119999999992</v>
       </c>
       <c r="E13">
         <v>51.7</v>
@@ -997,19 +997,19 @@
         <v>-6.800000000000001</v>
       </c>
       <c r="J13">
-        <v>-1.600400000000041</v>
+        <v>-1.600400000000046</v>
       </c>
       <c r="K13">
-        <v>5.199599999999959</v>
+        <v>5.199599999999954</v>
       </c>
       <c r="L13">
         <v>-7.039337474120083</v>
       </c>
       <c r="M13">
-        <v>-1.648829417655417</v>
+        <v>-1.648829417655423</v>
       </c>
       <c r="N13">
-        <v>5.390508056464666</v>
+        <v>5.39050805646466</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1607,25 +1607,25 @@
         <v>3.399999999999998</v>
       </c>
       <c r="H27">
-        <v>2.622800000000103</v>
+        <v>2.622800000000114</v>
       </c>
       <c r="I27">
         <v>8.000000000000002</v>
       </c>
       <c r="J27">
-        <v>0.3420000000001311</v>
+        <v>0.3420000000001255</v>
       </c>
       <c r="K27">
-        <v>7.657999999999871</v>
+        <v>7.657999999999881</v>
       </c>
       <c r="L27">
         <v>8.281573498964805</v>
       </c>
       <c r="M27">
-        <v>0.3512115772481972</v>
+        <v>0.3512115772481915</v>
       </c>
       <c r="N27">
-        <v>7.930361921716608</v>
+        <v>7.930361921716614</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1683,7 +1683,7 @@
         <v>45.5</v>
       </c>
       <c r="D29">
-        <v>48.30239999999993</v>
+        <v>48.30239999999994</v>
       </c>
       <c r="E29">
         <v>51.2</v>
@@ -1695,25 +1695,25 @@
         <v>3.299999999999992</v>
       </c>
       <c r="H29">
-        <v>2.940000000000176</v>
+        <v>2.940000000000165</v>
       </c>
       <c r="I29">
         <v>-5.699999999999999</v>
       </c>
       <c r="J29">
-        <v>-0.4551999999999556</v>
+        <v>-0.4551999999999501</v>
       </c>
       <c r="K29">
-        <v>5.244800000000044</v>
+        <v>5.244800000000049</v>
       </c>
       <c r="L29">
         <v>-5.894519131334022</v>
       </c>
       <c r="M29">
-        <v>-0.4689882546877771</v>
+        <v>-0.4689882546877713</v>
       </c>
       <c r="N29">
-        <v>5.425530876646245</v>
+        <v>5.42553087664625</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1739,25 +1739,25 @@
         <v>1.799999999999996</v>
       </c>
       <c r="H30">
-        <v>3.208400000000167</v>
+        <v>3.208400000000172</v>
       </c>
       <c r="I30">
         <v>8.600000000000001</v>
       </c>
       <c r="J30">
-        <v>-0.5244000000000582</v>
+        <v>-0.5244000000000526</v>
       </c>
       <c r="K30">
-        <v>9.12440000000006</v>
+        <v>9.124400000000049</v>
       </c>
       <c r="L30">
         <v>8.757637474541752</v>
       </c>
       <c r="M30">
-        <v>-0.5417825513784864</v>
+        <v>-0.5417825513784807</v>
       </c>
       <c r="N30">
-        <v>9.299420025920238</v>
+        <v>9.299420025920233</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -2041,13 +2041,13 @@
         <v>44.3</v>
       </c>
       <c r="F37">
-        <v>47.619831814436</v>
+        <v>47.61983181443601</v>
       </c>
       <c r="G37">
         <v>3.399999999999998</v>
       </c>
       <c r="H37">
-        <v>2.423429944016359</v>
+        <v>2.423429944016342</v>
       </c>
       <c r="I37">
         <v>8.000000000000002</v>
@@ -2062,10 +2062,10 @@
         <v>8.281573498964805</v>
       </c>
       <c r="M37">
-        <v>2.394946272215612</v>
+        <v>2.394946272215611</v>
       </c>
       <c r="N37">
-        <v>5.886627226749193</v>
+        <v>5.886627226749194</v>
       </c>
     </row>
     <row r="38" spans="1:14">
@@ -2091,25 +2091,25 @@
         <v>3.399999999999992</v>
       </c>
       <c r="H38">
-        <v>2.9081389957614</v>
+        <v>2.908138995761406</v>
       </c>
       <c r="I38">
         <v>-6.800000000000001</v>
       </c>
       <c r="J38">
-        <v>-1.255768581635441</v>
+        <v>-1.255768581635436</v>
       </c>
       <c r="K38">
-        <v>5.544231418364559</v>
+        <v>5.544231418364564</v>
       </c>
       <c r="L38">
         <v>-7.039337474120083</v>
       </c>
       <c r="M38">
-        <v>-1.293381925783275</v>
+        <v>-1.293381925783269</v>
       </c>
       <c r="N38">
-        <v>5.745955548336809</v>
+        <v>5.745955548336815</v>
       </c>
     </row>
     <row r="39" spans="1:14">
@@ -2123,19 +2123,19 @@
         <v>45.5</v>
       </c>
       <c r="D39">
-        <v>48.1056714755704</v>
+        <v>48.10567147557039</v>
       </c>
       <c r="E39">
         <v>51.2</v>
       </c>
       <c r="F39">
-        <v>48.95113339758257</v>
+        <v>48.95113339758256</v>
       </c>
       <c r="G39">
         <v>3.299999999999992</v>
       </c>
       <c r="H39">
-        <v>2.943195126847031</v>
+        <v>2.943195126847054</v>
       </c>
       <c r="I39">
         <v>-5.699999999999999</v>
@@ -2150,10 +2150,10 @@
         <v>-5.894519131334022</v>
       </c>
       <c r="M39">
-        <v>-0.8711000976357445</v>
+        <v>-0.8711000976357447</v>
       </c>
       <c r="N39">
-        <v>5.023419033698278</v>
+        <v>5.023419033698277</v>
       </c>
     </row>
     <row r="40" spans="1:14">
@@ -2167,37 +2167,37 @@
         <v>53.40000000000001</v>
       </c>
       <c r="D40">
-        <v>48.37637674792231</v>
+        <v>48.3763767479223</v>
       </c>
       <c r="E40">
         <v>44.8</v>
       </c>
       <c r="F40">
-        <v>48.43105651824637</v>
+        <v>48.43105651824636</v>
       </c>
       <c r="G40">
         <v>1.799999999999996</v>
       </c>
       <c r="H40">
-        <v>3.192566733831326</v>
+        <v>3.192566733831337</v>
       </c>
       <c r="I40">
         <v>8.600000000000001</v>
       </c>
       <c r="J40">
-        <v>-0.05467977032406757</v>
+        <v>-0.05467977032406202</v>
       </c>
       <c r="K40">
-        <v>8.654679770324075</v>
+        <v>8.654679770324064</v>
       </c>
       <c r="L40">
         <v>8.757637474541752</v>
       </c>
       <c r="M40">
-        <v>-0.05648302870888792</v>
+        <v>-0.05648302870888219</v>
       </c>
       <c r="N40">
-        <v>8.81412050325064</v>
+        <v>8.814120503250635</v>
       </c>
     </row>
     <row r="41" spans="1:14">
@@ -2229,19 +2229,19 @@
         <v>-2.700000000000002</v>
       </c>
       <c r="J41">
-        <v>-1.048624949950233</v>
+        <v>-1.048624949950228</v>
       </c>
       <c r="K41">
-        <v>1.651375050049769</v>
+        <v>1.651375050049775</v>
       </c>
       <c r="L41">
         <v>-2.774922918807813</v>
       </c>
       <c r="M41">
-        <v>-1.081718299630202</v>
+        <v>-1.081718299630196</v>
       </c>
       <c r="N41">
-        <v>1.693204619177612</v>
+        <v>1.693204619177617</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block2_Popular_Vote_Validation_v12.xlsx
+++ b/outputs/Block2_Popular_Vote_Validation_v12.xlsx
@@ -1657,19 +1657,19 @@
         <v>-6.800000000000001</v>
       </c>
       <c r="J28">
-        <v>-0.8272000000000279</v>
+        <v>-0.8272000000000224</v>
       </c>
       <c r="K28">
-        <v>5.972799999999973</v>
+        <v>5.972799999999978</v>
       </c>
       <c r="L28">
         <v>-7.039337474120083</v>
       </c>
       <c r="M28">
-        <v>-0.8516596655959444</v>
+        <v>-0.8516596655959388</v>
       </c>
       <c r="N28">
-        <v>6.187677808524139</v>
+        <v>6.187677808524144</v>
       </c>
     </row>
     <row r="29" spans="1:14">

--- a/outputs/Block2_Popular_Vote_Validation_v12.xlsx
+++ b/outputs/Block2_Popular_Vote_Validation_v12.xlsx
@@ -935,37 +935,37 @@
         <v>52.3</v>
       </c>
       <c r="D12">
-        <v>51.04320000000013</v>
+        <v>51.19840000000016</v>
       </c>
       <c r="E12">
         <v>44.3</v>
       </c>
       <c r="F12">
-        <v>46.73079999999982</v>
+        <v>46.6103999999998</v>
       </c>
       <c r="G12">
         <v>3.399999999999998</v>
       </c>
       <c r="H12">
-        <v>2.22600000000005</v>
+        <v>2.191200000000049</v>
       </c>
       <c r="I12">
         <v>8.000000000000002</v>
       </c>
       <c r="J12">
-        <v>4.312400000000316</v>
+        <v>4.588000000000358</v>
       </c>
       <c r="K12">
-        <v>3.687599999999685</v>
+        <v>3.411999999999643</v>
       </c>
       <c r="L12">
         <v>8.281573498964805</v>
       </c>
       <c r="M12">
-        <v>4.410579499662813</v>
+        <v>4.690784469291475</v>
       </c>
       <c r="N12">
-        <v>3.870993999301993</v>
+        <v>3.59078902967333</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -979,37 +979,37 @@
         <v>44.9</v>
       </c>
       <c r="D13">
-        <v>47.73119999999992</v>
+        <v>47.14879999999992</v>
       </c>
       <c r="E13">
         <v>51.7</v>
       </c>
       <c r="F13">
-        <v>49.33159999999997</v>
+        <v>49.93439999999999</v>
       </c>
       <c r="G13">
         <v>3.399999999999992</v>
       </c>
       <c r="H13">
-        <v>2.937200000000101</v>
+        <v>2.916800000000097</v>
       </c>
       <c r="I13">
         <v>-6.800000000000001</v>
       </c>
       <c r="J13">
-        <v>-1.600400000000046</v>
+        <v>-2.785600000000077</v>
       </c>
       <c r="K13">
-        <v>5.199599999999954</v>
+        <v>4.014399999999924</v>
       </c>
       <c r="L13">
         <v>-7.039337474120083</v>
       </c>
       <c r="M13">
-        <v>-1.648829417655423</v>
+        <v>-2.869291494305997</v>
       </c>
       <c r="N13">
-        <v>5.39050805646466</v>
+        <v>4.170045979814086</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1023,37 +1023,37 @@
         <v>45.5</v>
       </c>
       <c r="D14">
-        <v>47.95759999999995</v>
+        <v>48.67479999999995</v>
       </c>
       <c r="E14">
         <v>51.2</v>
       </c>
       <c r="F14">
-        <v>49.0967999999999</v>
+        <v>48.46919999999989</v>
       </c>
       <c r="G14">
         <v>3.299999999999992</v>
       </c>
       <c r="H14">
-        <v>2.945600000000143</v>
+        <v>2.856000000000164</v>
       </c>
       <c r="I14">
         <v>-5.699999999999999</v>
       </c>
       <c r="J14">
-        <v>-1.139199999999951</v>
+        <v>0.2056000000000724</v>
       </c>
       <c r="K14">
-        <v>4.560800000000048</v>
+        <v>5.905600000000072</v>
       </c>
       <c r="L14">
         <v>-5.894519131334022</v>
       </c>
       <c r="M14">
-        <v>-1.173774707792695</v>
+        <v>0.2116445688874997</v>
       </c>
       <c r="N14">
-        <v>4.720744423541327</v>
+        <v>6.106163700221521</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -1067,37 +1067,37 @@
         <v>53.40000000000001</v>
       </c>
       <c r="D15">
-        <v>48.6119999999999</v>
+        <v>49.03679999999988</v>
       </c>
       <c r="E15">
         <v>44.8</v>
       </c>
       <c r="F15">
-        <v>48.21079999999994</v>
+        <v>47.75599999999993</v>
       </c>
       <c r="G15">
         <v>1.799999999999996</v>
       </c>
       <c r="H15">
-        <v>3.177200000000169</v>
+        <v>3.207200000000193</v>
       </c>
       <c r="I15">
         <v>8.600000000000001</v>
       </c>
       <c r="J15">
-        <v>0.4011999999999627</v>
+        <v>1.280799999999954</v>
       </c>
       <c r="K15">
-        <v>8.198800000000034</v>
+        <v>7.319200000000054</v>
       </c>
       <c r="L15">
         <v>8.757637474541752</v>
       </c>
       <c r="M15">
-        <v>0.4143652114997329</v>
+        <v>1.323238918597206</v>
       </c>
       <c r="N15">
-        <v>8.343272263042019</v>
+        <v>7.434398555944546</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -1111,37 +1111,37 @@
         <v>47.3</v>
       </c>
       <c r="D16">
-        <v>47.59039999999992</v>
+        <v>46.4931999999999</v>
       </c>
       <c r="E16">
         <v>50</v>
       </c>
       <c r="F16">
-        <v>49.3047999999999</v>
+        <v>50.32159999999993</v>
       </c>
       <c r="G16">
         <v>2.700000000000002</v>
       </c>
       <c r="H16">
-        <v>3.104800000000174</v>
+        <v>3.185200000000166</v>
       </c>
       <c r="I16">
         <v>-2.700000000000002</v>
       </c>
       <c r="J16">
-        <v>-1.714399999999977</v>
+        <v>-3.828400000000032</v>
       </c>
       <c r="K16">
-        <v>0.9856000000000253</v>
+        <v>1.128400000000029</v>
       </c>
       <c r="L16">
         <v>-2.774922918807813</v>
       </c>
       <c r="M16">
-        <v>-1.769334291069093</v>
+        <v>-3.954354086358737</v>
       </c>
       <c r="N16">
-        <v>1.00558862773872</v>
+        <v>1.179431167550923</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1595,37 +1595,37 @@
         <v>52.3</v>
       </c>
       <c r="D27">
-        <v>48.85960000000001</v>
+        <v>49.03680000000003</v>
       </c>
       <c r="E27">
         <v>44.3</v>
       </c>
       <c r="F27">
-        <v>48.51759999999988</v>
+        <v>48.37719999999987</v>
       </c>
       <c r="G27">
         <v>3.399999999999998</v>
       </c>
       <c r="H27">
-        <v>2.622800000000114</v>
+        <v>2.586000000000088</v>
       </c>
       <c r="I27">
         <v>8.000000000000002</v>
       </c>
       <c r="J27">
-        <v>0.3420000000001255</v>
+        <v>0.6596000000001545</v>
       </c>
       <c r="K27">
-        <v>7.657999999999881</v>
+        <v>7.340399999999852</v>
       </c>
       <c r="L27">
         <v>8.281573498964805</v>
       </c>
       <c r="M27">
-        <v>0.3512115772481915</v>
+        <v>0.6771100663150627</v>
       </c>
       <c r="N27">
-        <v>7.930361921716614</v>
+        <v>7.604463432649743</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1639,37 +1639,37 @@
         <v>44.9</v>
       </c>
       <c r="D28">
-        <v>48.15039999999993</v>
+        <v>48.19359999999994</v>
       </c>
       <c r="E28">
         <v>51.7</v>
       </c>
       <c r="F28">
-        <v>48.97759999999995</v>
+        <v>48.94919999999995</v>
       </c>
       <c r="G28">
         <v>3.399999999999992</v>
       </c>
       <c r="H28">
-        <v>2.872000000000119</v>
+        <v>2.85720000000011</v>
       </c>
       <c r="I28">
         <v>-6.800000000000001</v>
       </c>
       <c r="J28">
-        <v>-0.8272000000000224</v>
+        <v>-0.7556000000000174</v>
       </c>
       <c r="K28">
-        <v>5.972799999999978</v>
+        <v>6.044399999999984</v>
       </c>
       <c r="L28">
         <v>-7.039337474120083</v>
       </c>
       <c r="M28">
-        <v>-0.8516596655959388</v>
+        <v>-0.7778239869553052</v>
       </c>
       <c r="N28">
-        <v>6.187677808524144</v>
+        <v>6.261513487164779</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1683,37 +1683,37 @@
         <v>45.5</v>
       </c>
       <c r="D29">
-        <v>48.30239999999994</v>
+        <v>48.46759999999996</v>
       </c>
       <c r="E29">
         <v>51.2</v>
       </c>
       <c r="F29">
-        <v>48.75759999999989</v>
+        <v>48.67959999999988</v>
       </c>
       <c r="G29">
         <v>3.299999999999992</v>
       </c>
       <c r="H29">
-        <v>2.940000000000165</v>
+        <v>2.852800000000155</v>
       </c>
       <c r="I29">
         <v>-5.699999999999999</v>
       </c>
       <c r="J29">
-        <v>-0.4551999999999501</v>
+        <v>-0.2119999999999178</v>
       </c>
       <c r="K29">
-        <v>5.244800000000049</v>
+        <v>5.488000000000081</v>
       </c>
       <c r="L29">
         <v>-5.894519131334022</v>
       </c>
       <c r="M29">
-        <v>-0.4689882546877713</v>
+        <v>-0.2182255381523278</v>
       </c>
       <c r="N29">
-        <v>5.42553087664625</v>
+        <v>5.676293593181694</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1727,37 +1727,37 @@
         <v>53.40000000000001</v>
       </c>
       <c r="D30">
-        <v>48.13359999999989</v>
+        <v>48.21359999999989</v>
       </c>
       <c r="E30">
         <v>44.8</v>
       </c>
       <c r="F30">
-        <v>48.65799999999994</v>
+        <v>48.56679999999993</v>
       </c>
       <c r="G30">
         <v>1.799999999999996</v>
       </c>
       <c r="H30">
-        <v>3.208400000000172</v>
+        <v>3.219600000000194</v>
       </c>
       <c r="I30">
         <v>8.600000000000001</v>
       </c>
       <c r="J30">
-        <v>-0.5244000000000526</v>
+        <v>-0.3532000000000424</v>
       </c>
       <c r="K30">
-        <v>9.124400000000049</v>
+        <v>8.953200000000045</v>
       </c>
       <c r="L30">
         <v>8.757637474541752</v>
       </c>
       <c r="M30">
-        <v>-0.5417825513784807</v>
+        <v>-0.3649499278780032</v>
       </c>
       <c r="N30">
-        <v>9.299420025920233</v>
+        <v>9.122587402419756</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1771,37 +1771,37 @@
         <v>47.3</v>
       </c>
       <c r="D31">
-        <v>48.41319999999995</v>
+        <v>47.49799999999993</v>
       </c>
       <c r="E31">
         <v>50</v>
       </c>
       <c r="F31">
-        <v>48.58719999999989</v>
+        <v>49.4347999999999</v>
       </c>
       <c r="G31">
         <v>2.700000000000002</v>
       </c>
       <c r="H31">
-        <v>2.999600000000152</v>
+        <v>3.067200000000164</v>
       </c>
       <c r="I31">
         <v>-2.700000000000002</v>
       </c>
       <c r="J31">
-        <v>-0.1739999999999353</v>
+        <v>-1.936799999999983</v>
       </c>
       <c r="K31">
-        <v>2.526000000000067</v>
+        <v>0.7632000000000194</v>
       </c>
       <c r="L31">
         <v>-2.774922918807813</v>
       </c>
       <c r="M31">
-        <v>-0.1793807035846611</v>
+        <v>-1.998085271445771</v>
       </c>
       <c r="N31">
-        <v>2.595542215223152</v>
+        <v>0.7768376473620424</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1815,37 +1815,37 @@
         <v>52.3</v>
       </c>
       <c r="D32">
-        <v>50.91721776896249</v>
+        <v>51.04021567738162</v>
       </c>
       <c r="E32">
         <v>44.3</v>
       </c>
       <c r="F32">
-        <v>46.89751498968565</v>
+        <v>46.82299388556208</v>
       </c>
       <c r="G32">
         <v>3.399999999999998</v>
       </c>
       <c r="H32">
-        <v>2.185267241351851</v>
+        <v>2.136790437056296</v>
       </c>
       <c r="I32">
         <v>8.000000000000002</v>
       </c>
       <c r="J32">
-        <v>4.019702779276846</v>
+        <v>4.217221791819531</v>
       </c>
       <c r="K32">
-        <v>3.980297220723156</v>
+        <v>3.782778208180471</v>
       </c>
       <c r="L32">
         <v>8.281573498964805</v>
       </c>
       <c r="M32">
-        <v>4.109506478124534</v>
+        <v>4.309302556756118</v>
       </c>
       <c r="N32">
-        <v>4.172067020840271</v>
+        <v>3.972270942208687</v>
       </c>
     </row>
     <row r="33" spans="1:14">
@@ -1859,37 +1859,37 @@
         <v>44.9</v>
       </c>
       <c r="D33">
-        <v>43.74621852868798</v>
+        <v>42.97111227691938</v>
       </c>
       <c r="E33">
         <v>51.7</v>
       </c>
       <c r="F33">
-        <v>53.04466286689375</v>
+        <v>53.51486110516986</v>
       </c>
       <c r="G33">
         <v>3.399999999999992</v>
       </c>
       <c r="H33">
-        <v>3.20911860441826</v>
+        <v>3.51402661791077</v>
       </c>
       <c r="I33">
         <v>-6.800000000000001</v>
       </c>
       <c r="J33">
-        <v>-9.298444338205769</v>
+        <v>-10.54374882825048</v>
       </c>
       <c r="K33">
-        <v>2.498444338205774</v>
+        <v>3.743748828250471</v>
       </c>
       <c r="L33">
         <v>-7.039337474120083</v>
       </c>
       <c r="M33">
-        <v>-9.606735886827268</v>
+        <v>-10.92775297658729</v>
       </c>
       <c r="N33">
-        <v>2.567398412707185</v>
+        <v>3.888415502467208</v>
       </c>
     </row>
     <row r="34" spans="1:14">
@@ -1903,37 +1903,37 @@
         <v>45.5</v>
       </c>
       <c r="D34">
-        <v>46.67102705793568</v>
+        <v>48.2279686201995</v>
       </c>
       <c r="E34">
         <v>51.2</v>
       </c>
       <c r="F34">
-        <v>50.15465217139654</v>
+        <v>48.88388413653071</v>
       </c>
       <c r="G34">
         <v>3.299999999999992</v>
       </c>
       <c r="H34">
-        <v>3.174320770667771</v>
+        <v>2.88814724326979</v>
       </c>
       <c r="I34">
         <v>-5.699999999999999</v>
       </c>
       <c r="J34">
-        <v>-3.483625113460858</v>
+        <v>-0.6559155163312069</v>
       </c>
       <c r="K34">
-        <v>2.216374886539141</v>
+        <v>5.044084483668793</v>
       </c>
       <c r="L34">
         <v>-5.894519131334022</v>
       </c>
       <c r="M34">
-        <v>-3.597831836748463</v>
+        <v>-0.6754227189695436</v>
       </c>
       <c r="N34">
-        <v>2.296687294585559</v>
+        <v>5.219096412364478</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1947,37 +1947,37 @@
         <v>53.40000000000001</v>
       </c>
       <c r="D35">
-        <v>49.88903282253776</v>
+        <v>48.28693426768441</v>
       </c>
       <c r="E35">
         <v>44.8</v>
       </c>
       <c r="F35">
-        <v>46.93095837053708</v>
+        <v>48.39573736435271</v>
       </c>
       <c r="G35">
         <v>1.799999999999996</v>
       </c>
       <c r="H35">
-        <v>3.180008806925167</v>
+        <v>3.317328367962885</v>
       </c>
       <c r="I35">
         <v>8.600000000000001</v>
       </c>
       <c r="J35">
-        <v>2.958074452000681</v>
+        <v>-0.1088030966683085</v>
       </c>
       <c r="K35">
-        <v>5.641925547999321</v>
+        <v>8.70880309666831</v>
       </c>
       <c r="L35">
         <v>8.757637474541752</v>
       </c>
       <c r="M35">
-        <v>3.055231069068989</v>
+        <v>-0.1125362951102554</v>
       </c>
       <c r="N35">
-        <v>5.702406405472764</v>
+        <v>8.870173769652007</v>
       </c>
     </row>
     <row r="36" spans="1:14">
@@ -1991,37 +1991,37 @@
         <v>47.3</v>
       </c>
       <c r="D36">
-        <v>48.13367072626829</v>
+        <v>47.58266216424929</v>
       </c>
       <c r="E36">
         <v>50</v>
       </c>
       <c r="F36">
-        <v>48.83034344642147</v>
+        <v>49.20824834711139</v>
       </c>
       <c r="G36">
         <v>2.700000000000002</v>
       </c>
       <c r="H36">
-        <v>3.035985827310244</v>
+        <v>3.209089488639322</v>
       </c>
       <c r="I36">
         <v>-2.700000000000002</v>
       </c>
       <c r="J36">
-        <v>-0.6966727201531853</v>
+        <v>-1.625586182862099</v>
       </c>
       <c r="K36">
-        <v>2.003327279846817</v>
+        <v>1.074413817137904</v>
       </c>
       <c r="L36">
         <v>-2.774922918807813</v>
       </c>
       <c r="M36">
-        <v>-0.7184858486906635</v>
+        <v>-1.67948227191364</v>
       </c>
       <c r="N36">
-        <v>2.05643707011715</v>
+        <v>1.095440646894173</v>
       </c>
     </row>
     <row r="37" spans="1:14">
@@ -2035,37 +2035,37 @@
         <v>52.3</v>
       </c>
       <c r="D37">
-        <v>49.95673824154764</v>
+        <v>50.07342175162359</v>
       </c>
       <c r="E37">
         <v>44.3</v>
       </c>
       <c r="F37">
-        <v>47.61983181443601</v>
+        <v>47.52990942321949</v>
       </c>
       <c r="G37">
         <v>3.399999999999998</v>
       </c>
       <c r="H37">
-        <v>2.423429944016342</v>
+        <v>2.396668825156922</v>
       </c>
       <c r="I37">
         <v>8.000000000000002</v>
       </c>
       <c r="J37">
-        <v>2.336906427111635</v>
+        <v>2.543512328404107</v>
       </c>
       <c r="K37">
-        <v>5.663093572888367</v>
+        <v>5.456487671595895</v>
       </c>
       <c r="L37">
         <v>8.281573498964805</v>
       </c>
       <c r="M37">
-        <v>2.394946272215611</v>
+        <v>2.605968769495942</v>
       </c>
       <c r="N37">
-        <v>5.886627226749194</v>
+        <v>5.675604729468864</v>
       </c>
     </row>
     <row r="38" spans="1:14">
@@ -2079,37 +2079,37 @@
         <v>44.9</v>
       </c>
       <c r="D38">
-        <v>47.91804621130158</v>
+        <v>47.60588018293675</v>
       </c>
       <c r="E38">
         <v>51.7</v>
       </c>
       <c r="F38">
-        <v>49.17381479293702</v>
+        <v>49.50339368661047</v>
       </c>
       <c r="G38">
         <v>3.399999999999992</v>
       </c>
       <c r="H38">
-        <v>2.908138995761406</v>
+        <v>2.890726130452786</v>
       </c>
       <c r="I38">
         <v>-6.800000000000001</v>
       </c>
       <c r="J38">
-        <v>-1.255768581635436</v>
+        <v>-1.89751350367372</v>
       </c>
       <c r="K38">
-        <v>5.544231418364564</v>
+        <v>4.90248649632628</v>
       </c>
       <c r="L38">
         <v>-7.039337474120083</v>
       </c>
       <c r="M38">
-        <v>-1.293381925783269</v>
+        <v>-1.953998241427245</v>
       </c>
       <c r="N38">
-        <v>5.745955548336815</v>
+        <v>5.085339232692839</v>
       </c>
     </row>
     <row r="39" spans="1:14">
@@ -2123,37 +2123,37 @@
         <v>45.5</v>
       </c>
       <c r="D39">
-        <v>48.10567147557039</v>
+        <v>48.59622591660155</v>
       </c>
       <c r="E39">
         <v>51.2</v>
       </c>
       <c r="F39">
-        <v>48.95113339758256</v>
+        <v>48.54898758275581</v>
       </c>
       <c r="G39">
         <v>3.299999999999992</v>
       </c>
       <c r="H39">
-        <v>2.943195126847054</v>
+        <v>2.854786500642642</v>
       </c>
       <c r="I39">
         <v>-5.699999999999999</v>
       </c>
       <c r="J39">
-        <v>-0.8454619220121695</v>
+        <v>0.04723833384575049</v>
       </c>
       <c r="K39">
-        <v>4.85453807798783</v>
+        <v>5.74723833384575</v>
       </c>
       <c r="L39">
         <v>-5.894519131334022</v>
       </c>
       <c r="M39">
-        <v>-0.8711000976357447</v>
+        <v>0.04862651709140871</v>
       </c>
       <c r="N39">
-        <v>5.023419033698277</v>
+        <v>5.94314564842543</v>
       </c>
     </row>
     <row r="40" spans="1:14">
@@ -2167,37 +2167,37 @@
         <v>53.40000000000001</v>
       </c>
       <c r="D40">
-        <v>48.3763767479223</v>
+        <v>48.61041134543477</v>
       </c>
       <c r="E40">
         <v>44.8</v>
       </c>
       <c r="F40">
-        <v>48.43105651824636</v>
+        <v>48.175965890575</v>
       </c>
       <c r="G40">
         <v>1.799999999999996</v>
       </c>
       <c r="H40">
-        <v>3.192566733831337</v>
+        <v>3.213622763990232</v>
       </c>
       <c r="I40">
         <v>8.600000000000001</v>
       </c>
       <c r="J40">
-        <v>-0.05467977032406202</v>
+        <v>0.4344454548597665</v>
       </c>
       <c r="K40">
-        <v>8.654679770324064</v>
+        <v>8.165554545140235</v>
       </c>
       <c r="L40">
         <v>8.757637474541752</v>
       </c>
       <c r="M40">
-        <v>-0.05648302870888219</v>
+        <v>0.4488704580815008</v>
       </c>
       <c r="N40">
-        <v>8.814120503250635</v>
+        <v>8.308767016460251</v>
       </c>
     </row>
     <row r="41" spans="1:14">
@@ -2211,37 +2211,37 @@
         <v>47.3</v>
       </c>
       <c r="D41">
-        <v>47.94602172888914</v>
+        <v>46.89868167698049</v>
       </c>
       <c r="E41">
         <v>50</v>
       </c>
       <c r="F41">
-        <v>48.99464667883937</v>
+        <v>49.96373659320616</v>
       </c>
       <c r="G41">
         <v>2.700000000000002</v>
       </c>
       <c r="H41">
-        <v>3.059331592271502</v>
+        <v>3.137581729813355</v>
       </c>
       <c r="I41">
         <v>-2.700000000000002</v>
       </c>
       <c r="J41">
-        <v>-1.048624949950228</v>
+        <v>-3.065054916225662</v>
       </c>
       <c r="K41">
-        <v>1.651375050049775</v>
+        <v>0.36505491622566</v>
       </c>
       <c r="L41">
         <v>-2.774922918807813</v>
       </c>
       <c r="M41">
-        <v>-1.081718299630196</v>
+        <v>-3.164338626851172</v>
       </c>
       <c r="N41">
-        <v>1.693204619177617</v>
+        <v>0.3894157080433582</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block2_Popular_Vote_Validation_v12.xlsx
+++ b/outputs/Block2_Popular_Vote_Validation_v12.xlsx
@@ -2167,19 +2167,19 @@
         <v>53.40000000000001</v>
       </c>
       <c r="D40">
-        <v>48.61041134543477</v>
+        <v>48.61041134543476</v>
       </c>
       <c r="E40">
         <v>44.8</v>
       </c>
       <c r="F40">
-        <v>48.175965890575</v>
+        <v>48.17596589057499</v>
       </c>
       <c r="G40">
         <v>1.799999999999996</v>
       </c>
       <c r="H40">
-        <v>3.213622763990232</v>
+        <v>3.213622763990254</v>
       </c>
       <c r="I40">
         <v>8.600000000000001</v>
@@ -2194,7 +2194,7 @@
         <v>8.757637474541752</v>
       </c>
       <c r="M40">
-        <v>0.4488704580815008</v>
+        <v>0.4488704580815009</v>
       </c>
       <c r="N40">
         <v>8.308767016460251</v>

--- a/outputs/Block2_Popular_Vote_Validation_v12.xlsx
+++ b/outputs/Block2_Popular_Vote_Validation_v12.xlsx
@@ -2167,19 +2167,19 @@
         <v>53.40000000000001</v>
       </c>
       <c r="D40">
-        <v>48.61041134543476</v>
+        <v>48.61041134543477</v>
       </c>
       <c r="E40">
         <v>44.8</v>
       </c>
       <c r="F40">
-        <v>48.17596589057499</v>
+        <v>48.175965890575</v>
       </c>
       <c r="G40">
         <v>1.799999999999996</v>
       </c>
       <c r="H40">
-        <v>3.213622763990254</v>
+        <v>3.213622763990232</v>
       </c>
       <c r="I40">
         <v>8.600000000000001</v>
@@ -2194,7 +2194,7 @@
         <v>8.757637474541752</v>
       </c>
       <c r="M40">
-        <v>0.4488704580815009</v>
+        <v>0.4488704580815008</v>
       </c>
       <c r="N40">
         <v>8.308767016460251</v>

--- a/outputs/Block2_Popular_Vote_Validation_v12.xlsx
+++ b/outputs/Block2_Popular_Vote_Validation_v12.xlsx
@@ -2035,7 +2035,7 @@
         <v>52.3</v>
       </c>
       <c r="D37">
-        <v>50.07342175162359</v>
+        <v>50.07342175162361</v>
       </c>
       <c r="E37">
         <v>44.3</v>
@@ -2047,25 +2047,25 @@
         <v>3.399999999999998</v>
       </c>
       <c r="H37">
-        <v>2.396668825156922</v>
+        <v>2.396668825156911</v>
       </c>
       <c r="I37">
         <v>8.000000000000002</v>
       </c>
       <c r="J37">
-        <v>2.543512328404107</v>
+        <v>2.543512328404118</v>
       </c>
       <c r="K37">
-        <v>5.456487671595895</v>
+        <v>5.456487671595883</v>
       </c>
       <c r="L37">
         <v>8.281573498964805</v>
       </c>
       <c r="M37">
-        <v>2.605968769495942</v>
+        <v>2.605968769495953</v>
       </c>
       <c r="N37">
-        <v>5.675604729468864</v>
+        <v>5.675604729468852</v>
       </c>
     </row>
     <row r="38" spans="1:14">
@@ -2079,7 +2079,7 @@
         <v>44.9</v>
       </c>
       <c r="D38">
-        <v>47.60588018293675</v>
+        <v>47.60588018293674</v>
       </c>
       <c r="E38">
         <v>51.7</v>
@@ -2091,7 +2091,7 @@
         <v>3.399999999999992</v>
       </c>
       <c r="H38">
-        <v>2.890726130452786</v>
+        <v>2.890726130452792</v>
       </c>
       <c r="I38">
         <v>-6.800000000000001</v>
@@ -2109,7 +2109,7 @@
         <v>-1.953998241427245</v>
       </c>
       <c r="N38">
-        <v>5.085339232692839</v>
+        <v>5.085339232692838</v>
       </c>
     </row>
     <row r="39" spans="1:14">
@@ -2167,19 +2167,19 @@
         <v>53.40000000000001</v>
       </c>
       <c r="D40">
-        <v>48.61041134543477</v>
+        <v>48.61041134543476</v>
       </c>
       <c r="E40">
         <v>44.8</v>
       </c>
       <c r="F40">
-        <v>48.175965890575</v>
+        <v>48.17596589057499</v>
       </c>
       <c r="G40">
         <v>1.799999999999996</v>
       </c>
       <c r="H40">
-        <v>3.213622763990232</v>
+        <v>3.213622763990254</v>
       </c>
       <c r="I40">
         <v>8.600000000000001</v>
@@ -2194,7 +2194,7 @@
         <v>8.757637474541752</v>
       </c>
       <c r="M40">
-        <v>0.4488704580815008</v>
+        <v>0.4488704580815009</v>
       </c>
       <c r="N40">
         <v>8.308767016460251</v>

--- a/outputs/Block2_Popular_Vote_Validation_v12.xlsx
+++ b/outputs/Block2_Popular_Vote_Validation_v12.xlsx
@@ -2035,7 +2035,7 @@
         <v>52.3</v>
       </c>
       <c r="D37">
-        <v>50.07342175162361</v>
+        <v>50.07342175162359</v>
       </c>
       <c r="E37">
         <v>44.3</v>
@@ -2047,25 +2047,25 @@
         <v>3.399999999999998</v>
       </c>
       <c r="H37">
-        <v>2.396668825156911</v>
+        <v>2.396668825156922</v>
       </c>
       <c r="I37">
         <v>8.000000000000002</v>
       </c>
       <c r="J37">
-        <v>2.543512328404118</v>
+        <v>2.543512328404107</v>
       </c>
       <c r="K37">
-        <v>5.456487671595883</v>
+        <v>5.456487671595895</v>
       </c>
       <c r="L37">
         <v>8.281573498964805</v>
       </c>
       <c r="M37">
-        <v>2.605968769495953</v>
+        <v>2.605968769495942</v>
       </c>
       <c r="N37">
-        <v>5.675604729468852</v>
+        <v>5.675604729468864</v>
       </c>
     </row>
     <row r="38" spans="1:14">
@@ -2079,7 +2079,7 @@
         <v>44.9</v>
       </c>
       <c r="D38">
-        <v>47.60588018293674</v>
+        <v>47.60588018293675</v>
       </c>
       <c r="E38">
         <v>51.7</v>
@@ -2091,7 +2091,7 @@
         <v>3.399999999999992</v>
       </c>
       <c r="H38">
-        <v>2.890726130452792</v>
+        <v>2.890726130452786</v>
       </c>
       <c r="I38">
         <v>-6.800000000000001</v>
@@ -2109,7 +2109,7 @@
         <v>-1.953998241427245</v>
       </c>
       <c r="N38">
-        <v>5.085339232692838</v>
+        <v>5.085339232692839</v>
       </c>
     </row>
     <row r="39" spans="1:14">

--- a/outputs/Block2_Popular_Vote_Validation_v12.xlsx
+++ b/outputs/Block2_Popular_Vote_Validation_v12.xlsx
@@ -1683,7 +1683,7 @@
         <v>45.5</v>
       </c>
       <c r="D29">
-        <v>48.46759999999996</v>
+        <v>48.46759999999995</v>
       </c>
       <c r="E29">
         <v>51.2</v>
@@ -1695,25 +1695,25 @@
         <v>3.299999999999992</v>
       </c>
       <c r="H29">
-        <v>2.852800000000155</v>
+        <v>2.852800000000166</v>
       </c>
       <c r="I29">
         <v>-5.699999999999999</v>
       </c>
       <c r="J29">
-        <v>-0.2119999999999178</v>
+        <v>-0.2119999999999234</v>
       </c>
       <c r="K29">
-        <v>5.488000000000081</v>
+        <v>5.488000000000076</v>
       </c>
       <c r="L29">
         <v>-5.894519131334022</v>
       </c>
       <c r="M29">
-        <v>-0.2182255381523278</v>
+        <v>-0.2182255381523335</v>
       </c>
       <c r="N29">
-        <v>5.676293593181694</v>
+        <v>5.676293593181688</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -2079,7 +2079,7 @@
         <v>44.9</v>
       </c>
       <c r="D38">
-        <v>47.60588018293675</v>
+        <v>47.60588018293676</v>
       </c>
       <c r="E38">
         <v>51.7</v>
@@ -2091,7 +2091,7 @@
         <v>3.399999999999992</v>
       </c>
       <c r="H38">
-        <v>2.890726130452786</v>
+        <v>2.89072613045277</v>
       </c>
       <c r="I38">
         <v>-6.800000000000001</v>
@@ -2141,19 +2141,19 @@
         <v>-5.699999999999999</v>
       </c>
       <c r="J39">
-        <v>0.04723833384575049</v>
+        <v>0.04723833384574494</v>
       </c>
       <c r="K39">
-        <v>5.74723833384575</v>
+        <v>5.747238333845744</v>
       </c>
       <c r="L39">
         <v>-5.894519131334022</v>
       </c>
       <c r="M39">
-        <v>0.04862651709140871</v>
+        <v>0.048626517091403</v>
       </c>
       <c r="N39">
-        <v>5.94314564842543</v>
+        <v>5.943145648425425</v>
       </c>
     </row>
     <row r="40" spans="1:14">

--- a/outputs/Block2_Popular_Vote_Validation_v12.xlsx
+++ b/outputs/Block2_Popular_Vote_Validation_v12.xlsx
@@ -1683,7 +1683,7 @@
         <v>45.5</v>
       </c>
       <c r="D29">
-        <v>48.46759999999995</v>
+        <v>48.46759999999996</v>
       </c>
       <c r="E29">
         <v>51.2</v>
@@ -1695,25 +1695,25 @@
         <v>3.299999999999992</v>
       </c>
       <c r="H29">
-        <v>2.852800000000166</v>
+        <v>2.852800000000155</v>
       </c>
       <c r="I29">
         <v>-5.699999999999999</v>
       </c>
       <c r="J29">
-        <v>-0.2119999999999234</v>
+        <v>-0.2119999999999178</v>
       </c>
       <c r="K29">
-        <v>5.488000000000076</v>
+        <v>5.488000000000081</v>
       </c>
       <c r="L29">
         <v>-5.894519131334022</v>
       </c>
       <c r="M29">
-        <v>-0.2182255381523335</v>
+        <v>-0.2182255381523278</v>
       </c>
       <c r="N29">
-        <v>5.676293593181688</v>
+        <v>5.676293593181694</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -2079,7 +2079,7 @@
         <v>44.9</v>
       </c>
       <c r="D38">
-        <v>47.60588018293676</v>
+        <v>47.60588018293675</v>
       </c>
       <c r="E38">
         <v>51.7</v>
@@ -2091,7 +2091,7 @@
         <v>3.399999999999992</v>
       </c>
       <c r="H38">
-        <v>2.89072613045277</v>
+        <v>2.890726130452786</v>
       </c>
       <c r="I38">
         <v>-6.800000000000001</v>
@@ -2141,19 +2141,19 @@
         <v>-5.699999999999999</v>
       </c>
       <c r="J39">
-        <v>0.04723833384574494</v>
+        <v>0.04723833384575049</v>
       </c>
       <c r="K39">
-        <v>5.747238333845744</v>
+        <v>5.74723833384575</v>
       </c>
       <c r="L39">
         <v>-5.894519131334022</v>
       </c>
       <c r="M39">
-        <v>0.048626517091403</v>
+        <v>0.04862651709140871</v>
       </c>
       <c r="N39">
-        <v>5.943145648425425</v>
+        <v>5.94314564842543</v>
       </c>
     </row>
     <row r="40" spans="1:14">

--- a/outputs/Block2_Popular_Vote_Validation_v12.xlsx
+++ b/outputs/Block2_Popular_Vote_Validation_v12.xlsx
@@ -1683,7 +1683,7 @@
         <v>45.5</v>
       </c>
       <c r="D29">
-        <v>48.46759999999996</v>
+        <v>48.46759999999995</v>
       </c>
       <c r="E29">
         <v>51.2</v>
@@ -1695,25 +1695,25 @@
         <v>3.299999999999992</v>
       </c>
       <c r="H29">
-        <v>2.852800000000155</v>
+        <v>2.852800000000166</v>
       </c>
       <c r="I29">
         <v>-5.699999999999999</v>
       </c>
       <c r="J29">
-        <v>-0.2119999999999178</v>
+        <v>-0.2119999999999234</v>
       </c>
       <c r="K29">
-        <v>5.488000000000081</v>
+        <v>5.488000000000076</v>
       </c>
       <c r="L29">
         <v>-5.894519131334022</v>
       </c>
       <c r="M29">
-        <v>-0.2182255381523278</v>
+        <v>-0.2182255381523335</v>
       </c>
       <c r="N29">
-        <v>5.676293593181694</v>
+        <v>5.676293593181688</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -2141,19 +2141,19 @@
         <v>-5.699999999999999</v>
       </c>
       <c r="J39">
-        <v>0.04723833384575049</v>
+        <v>0.04723833384574494</v>
       </c>
       <c r="K39">
-        <v>5.74723833384575</v>
+        <v>5.747238333845744</v>
       </c>
       <c r="L39">
         <v>-5.894519131334022</v>
       </c>
       <c r="M39">
-        <v>0.04862651709140871</v>
+        <v>0.048626517091403</v>
       </c>
       <c r="N39">
-        <v>5.94314564842543</v>
+        <v>5.943145648425425</v>
       </c>
     </row>
     <row r="40" spans="1:14">

--- a/outputs/Block2_Popular_Vote_Validation_v12.xlsx
+++ b/outputs/Block2_Popular_Vote_Validation_v12.xlsx
@@ -1111,7 +1111,7 @@
         <v>47.3</v>
       </c>
       <c r="D16">
-        <v>46.4931999999999</v>
+        <v>46.49319999999991</v>
       </c>
       <c r="E16">
         <v>50</v>
@@ -1129,7 +1129,7 @@
         <v>-2.700000000000002</v>
       </c>
       <c r="J16">
-        <v>-3.828400000000032</v>
+        <v>-3.828400000000026</v>
       </c>
       <c r="K16">
         <v>1.128400000000029</v>
@@ -1138,10 +1138,10 @@
         <v>-2.774922918807813</v>
       </c>
       <c r="M16">
-        <v>-3.954354086358737</v>
+        <v>-3.95435408635873</v>
       </c>
       <c r="N16">
-        <v>1.179431167550923</v>
+        <v>1.179431167550917</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1739,25 +1739,25 @@
         <v>1.799999999999996</v>
       </c>
       <c r="H30">
-        <v>3.219600000000194</v>
+        <v>3.219600000000184</v>
       </c>
       <c r="I30">
         <v>8.600000000000001</v>
       </c>
       <c r="J30">
-        <v>-0.3532000000000424</v>
+        <v>-0.3532000000000368</v>
       </c>
       <c r="K30">
-        <v>8.953200000000045</v>
+        <v>8.953200000000033</v>
       </c>
       <c r="L30">
         <v>8.757637474541752</v>
       </c>
       <c r="M30">
-        <v>-0.3649499278780032</v>
+        <v>-0.3649499278779975</v>
       </c>
       <c r="N30">
-        <v>9.122587402419756</v>
+        <v>9.12258740241975</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -2035,7 +2035,7 @@
         <v>52.3</v>
       </c>
       <c r="D37">
-        <v>50.07342175162359</v>
+        <v>50.07342175162361</v>
       </c>
       <c r="E37">
         <v>44.3</v>
@@ -2047,25 +2047,25 @@
         <v>3.399999999999998</v>
       </c>
       <c r="H37">
-        <v>2.396668825156922</v>
+        <v>2.396668825156911</v>
       </c>
       <c r="I37">
         <v>8.000000000000002</v>
       </c>
       <c r="J37">
-        <v>2.543512328404107</v>
+        <v>2.543512328404118</v>
       </c>
       <c r="K37">
-        <v>5.456487671595895</v>
+        <v>5.456487671595883</v>
       </c>
       <c r="L37">
         <v>8.281573498964805</v>
       </c>
       <c r="M37">
-        <v>2.605968769495942</v>
+        <v>2.605968769495953</v>
       </c>
       <c r="N37">
-        <v>5.675604729468864</v>
+        <v>5.675604729468852</v>
       </c>
     </row>
     <row r="38" spans="1:14">
@@ -2167,19 +2167,19 @@
         <v>53.40000000000001</v>
       </c>
       <c r="D40">
-        <v>48.61041134543476</v>
+        <v>48.61041134543477</v>
       </c>
       <c r="E40">
         <v>44.8</v>
       </c>
       <c r="F40">
-        <v>48.17596589057499</v>
+        <v>48.175965890575</v>
       </c>
       <c r="G40">
         <v>1.799999999999996</v>
       </c>
       <c r="H40">
-        <v>3.213622763990254</v>
+        <v>3.213622763990232</v>
       </c>
       <c r="I40">
         <v>8.600000000000001</v>
@@ -2194,7 +2194,7 @@
         <v>8.757637474541752</v>
       </c>
       <c r="M40">
-        <v>0.4488704580815009</v>
+        <v>0.4488704580815008</v>
       </c>
       <c r="N40">
         <v>8.308767016460251</v>
@@ -2217,31 +2217,31 @@
         <v>50</v>
       </c>
       <c r="F41">
-        <v>49.96373659320616</v>
+        <v>49.96373659320615</v>
       </c>
       <c r="G41">
         <v>2.700000000000002</v>
       </c>
       <c r="H41">
-        <v>3.137581729813355</v>
+        <v>3.13758172981336</v>
       </c>
       <c r="I41">
         <v>-2.700000000000002</v>
       </c>
       <c r="J41">
-        <v>-3.065054916225662</v>
+        <v>-3.065054916225657</v>
       </c>
       <c r="K41">
-        <v>0.36505491622566</v>
+        <v>0.3650549162256489</v>
       </c>
       <c r="L41">
         <v>-2.774922918807813</v>
       </c>
       <c r="M41">
-        <v>-3.164338626851172</v>
+        <v>-3.164338626851166</v>
       </c>
       <c r="N41">
-        <v>0.3894157080433582</v>
+        <v>0.3894157080433525</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block2_Popular_Vote_Validation_v12.xlsx
+++ b/outputs/Block2_Popular_Vote_Validation_v12.xlsx
@@ -1601,19 +1601,19 @@
         <v>44.3</v>
       </c>
       <c r="F27">
-        <v>48.37719999999987</v>
+        <v>48.37719999999988</v>
       </c>
       <c r="G27">
         <v>3.399999999999998</v>
       </c>
       <c r="H27">
-        <v>2.586000000000088</v>
+        <v>2.586000000000083</v>
       </c>
       <c r="I27">
         <v>8.000000000000002</v>
       </c>
       <c r="J27">
-        <v>0.6596000000001545</v>
+        <v>0.659600000000149</v>
       </c>
       <c r="K27">
         <v>7.340399999999852</v>
@@ -1622,10 +1622,10 @@
         <v>8.281573498964805</v>
       </c>
       <c r="M27">
-        <v>0.6771100663150627</v>
+        <v>0.6771100663150569</v>
       </c>
       <c r="N27">
-        <v>7.604463432649743</v>
+        <v>7.604463432649748</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1695,25 +1695,25 @@
         <v>3.299999999999992</v>
       </c>
       <c r="H29">
-        <v>2.852800000000166</v>
+        <v>2.852800000000177</v>
       </c>
       <c r="I29">
         <v>-5.699999999999999</v>
       </c>
       <c r="J29">
-        <v>-0.2119999999999234</v>
+        <v>-0.2119999999999289</v>
       </c>
       <c r="K29">
-        <v>5.488000000000076</v>
+        <v>5.488000000000071</v>
       </c>
       <c r="L29">
         <v>-5.894519131334022</v>
       </c>
       <c r="M29">
-        <v>-0.2182255381523335</v>
+        <v>-0.2182255381523392</v>
       </c>
       <c r="N29">
-        <v>5.676293593181688</v>
+        <v>5.676293593181683</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1739,25 +1739,25 @@
         <v>1.799999999999996</v>
       </c>
       <c r="H30">
-        <v>3.219600000000184</v>
+        <v>3.219600000000194</v>
       </c>
       <c r="I30">
         <v>8.600000000000001</v>
       </c>
       <c r="J30">
-        <v>-0.3532000000000368</v>
+        <v>-0.3532000000000424</v>
       </c>
       <c r="K30">
-        <v>8.953200000000033</v>
+        <v>8.953200000000045</v>
       </c>
       <c r="L30">
         <v>8.757637474541752</v>
       </c>
       <c r="M30">
-        <v>-0.3649499278779975</v>
+        <v>-0.3649499278780032</v>
       </c>
       <c r="N30">
-        <v>9.12258740241975</v>
+        <v>9.122587402419756</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -2079,7 +2079,7 @@
         <v>44.9</v>
       </c>
       <c r="D38">
-        <v>47.60588018293675</v>
+        <v>47.60588018293676</v>
       </c>
       <c r="E38">
         <v>51.7</v>
@@ -2091,7 +2091,7 @@
         <v>3.399999999999992</v>
       </c>
       <c r="H38">
-        <v>2.890726130452786</v>
+        <v>2.89072613045277</v>
       </c>
       <c r="I38">
         <v>-6.800000000000001</v>
@@ -2123,19 +2123,19 @@
         <v>45.5</v>
       </c>
       <c r="D39">
-        <v>48.59622591660155</v>
+        <v>48.59622591660154</v>
       </c>
       <c r="E39">
         <v>51.2</v>
       </c>
       <c r="F39">
-        <v>48.54898758275581</v>
+        <v>48.5489875827558</v>
       </c>
       <c r="G39">
         <v>3.299999999999992</v>
       </c>
       <c r="H39">
-        <v>2.854786500642642</v>
+        <v>2.854786500642659</v>
       </c>
       <c r="I39">
         <v>-5.699999999999999</v>
@@ -2150,7 +2150,7 @@
         <v>-5.894519131334022</v>
       </c>
       <c r="M39">
-        <v>0.048626517091403</v>
+        <v>0.04862651709140301</v>
       </c>
       <c r="N39">
         <v>5.943145648425425</v>
@@ -2217,31 +2217,31 @@
         <v>50</v>
       </c>
       <c r="F41">
-        <v>49.96373659320615</v>
+        <v>49.96373659320616</v>
       </c>
       <c r="G41">
         <v>2.700000000000002</v>
       </c>
       <c r="H41">
-        <v>3.13758172981336</v>
+        <v>3.137581729813355</v>
       </c>
       <c r="I41">
         <v>-2.700000000000002</v>
       </c>
       <c r="J41">
-        <v>-3.065054916225657</v>
+        <v>-3.065054916225662</v>
       </c>
       <c r="K41">
-        <v>0.3650549162256489</v>
+        <v>0.36505491622566</v>
       </c>
       <c r="L41">
         <v>-2.774922918807813</v>
       </c>
       <c r="M41">
-        <v>-3.164338626851166</v>
+        <v>-3.164338626851172</v>
       </c>
       <c r="N41">
-        <v>0.3894157080433525</v>
+        <v>0.3894157080433582</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block2_Popular_Vote_Validation_v12.xlsx
+++ b/outputs/Block2_Popular_Vote_Validation_v12.xlsx
@@ -1111,7 +1111,7 @@
         <v>47.3</v>
       </c>
       <c r="D16">
-        <v>46.49319999999991</v>
+        <v>46.4931999999999</v>
       </c>
       <c r="E16">
         <v>50</v>
@@ -1129,7 +1129,7 @@
         <v>-2.700000000000002</v>
       </c>
       <c r="J16">
-        <v>-3.828400000000026</v>
+        <v>-3.828400000000032</v>
       </c>
       <c r="K16">
         <v>1.128400000000029</v>
@@ -1138,10 +1138,10 @@
         <v>-2.774922918807813</v>
       </c>
       <c r="M16">
-        <v>-3.95435408635873</v>
+        <v>-3.954354086358737</v>
       </c>
       <c r="N16">
-        <v>1.179431167550917</v>
+        <v>1.179431167550923</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1601,19 +1601,19 @@
         <v>44.3</v>
       </c>
       <c r="F27">
-        <v>48.37719999999988</v>
+        <v>48.37719999999987</v>
       </c>
       <c r="G27">
         <v>3.399999999999998</v>
       </c>
       <c r="H27">
-        <v>2.586000000000083</v>
+        <v>2.586000000000088</v>
       </c>
       <c r="I27">
         <v>8.000000000000002</v>
       </c>
       <c r="J27">
-        <v>0.659600000000149</v>
+        <v>0.6596000000001545</v>
       </c>
       <c r="K27">
         <v>7.340399999999852</v>
@@ -1622,10 +1622,10 @@
         <v>8.281573498964805</v>
       </c>
       <c r="M27">
-        <v>0.6771100663150569</v>
+        <v>0.6771100663150627</v>
       </c>
       <c r="N27">
-        <v>7.604463432649748</v>
+        <v>7.604463432649743</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -1683,7 +1683,7 @@
         <v>45.5</v>
       </c>
       <c r="D29">
-        <v>48.46759999999995</v>
+        <v>48.46759999999996</v>
       </c>
       <c r="E29">
         <v>51.2</v>
@@ -1695,25 +1695,25 @@
         <v>3.299999999999992</v>
       </c>
       <c r="H29">
-        <v>2.852800000000177</v>
+        <v>2.852800000000155</v>
       </c>
       <c r="I29">
         <v>-5.699999999999999</v>
       </c>
       <c r="J29">
-        <v>-0.2119999999999289</v>
+        <v>-0.2119999999999178</v>
       </c>
       <c r="K29">
-        <v>5.488000000000071</v>
+        <v>5.488000000000081</v>
       </c>
       <c r="L29">
         <v>-5.894519131334022</v>
       </c>
       <c r="M29">
-        <v>-0.2182255381523392</v>
+        <v>-0.2182255381523278</v>
       </c>
       <c r="N29">
-        <v>5.676293593181683</v>
+        <v>5.676293593181694</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -2035,7 +2035,7 @@
         <v>52.3</v>
       </c>
       <c r="D37">
-        <v>50.07342175162361</v>
+        <v>50.07342175162359</v>
       </c>
       <c r="E37">
         <v>44.3</v>
@@ -2047,25 +2047,25 @@
         <v>3.399999999999998</v>
       </c>
       <c r="H37">
-        <v>2.396668825156911</v>
+        <v>2.396668825156922</v>
       </c>
       <c r="I37">
         <v>8.000000000000002</v>
       </c>
       <c r="J37">
-        <v>2.543512328404118</v>
+        <v>2.543512328404107</v>
       </c>
       <c r="K37">
-        <v>5.456487671595883</v>
+        <v>5.456487671595895</v>
       </c>
       <c r="L37">
         <v>8.281573498964805</v>
       </c>
       <c r="M37">
-        <v>2.605968769495953</v>
+        <v>2.605968769495942</v>
       </c>
       <c r="N37">
-        <v>5.675604729468852</v>
+        <v>5.675604729468864</v>
       </c>
     </row>
     <row r="38" spans="1:14">
@@ -2079,7 +2079,7 @@
         <v>44.9</v>
       </c>
       <c r="D38">
-        <v>47.60588018293676</v>
+        <v>47.60588018293675</v>
       </c>
       <c r="E38">
         <v>51.7</v>
@@ -2091,7 +2091,7 @@
         <v>3.399999999999992</v>
       </c>
       <c r="H38">
-        <v>2.89072613045277</v>
+        <v>2.890726130452786</v>
       </c>
       <c r="I38">
         <v>-6.800000000000001</v>
@@ -2123,37 +2123,37 @@
         <v>45.5</v>
       </c>
       <c r="D39">
-        <v>48.59622591660154</v>
+        <v>48.59622591660155</v>
       </c>
       <c r="E39">
         <v>51.2</v>
       </c>
       <c r="F39">
-        <v>48.5489875827558</v>
+        <v>48.54898758275581</v>
       </c>
       <c r="G39">
         <v>3.299999999999992</v>
       </c>
       <c r="H39">
-        <v>2.854786500642659</v>
+        <v>2.854786500642642</v>
       </c>
       <c r="I39">
         <v>-5.699999999999999</v>
       </c>
       <c r="J39">
-        <v>0.04723833384574494</v>
+        <v>0.04723833384575049</v>
       </c>
       <c r="K39">
-        <v>5.747238333845744</v>
+        <v>5.74723833384575</v>
       </c>
       <c r="L39">
         <v>-5.894519131334022</v>
       </c>
       <c r="M39">
-        <v>0.04862651709140301</v>
+        <v>0.04862651709140871</v>
       </c>
       <c r="N39">
-        <v>5.943145648425425</v>
+        <v>5.94314564842543</v>
       </c>
     </row>
     <row r="40" spans="1:14">

--- a/outputs/Block2_Popular_Vote_Validation_v12.xlsx
+++ b/outputs/Block2_Popular_Vote_Validation_v12.xlsx
@@ -2217,31 +2217,31 @@
         <v>50</v>
       </c>
       <c r="F41">
-        <v>49.96373659320616</v>
+        <v>49.96373659320614</v>
       </c>
       <c r="G41">
         <v>2.700000000000002</v>
       </c>
       <c r="H41">
-        <v>3.137581729813355</v>
+        <v>3.137581729813366</v>
       </c>
       <c r="I41">
         <v>-2.700000000000002</v>
       </c>
       <c r="J41">
-        <v>-3.065054916225662</v>
+        <v>-3.065054916225651</v>
       </c>
       <c r="K41">
-        <v>0.36505491622566</v>
+        <v>0.3650549162256489</v>
       </c>
       <c r="L41">
         <v>-2.774922918807813</v>
       </c>
       <c r="M41">
-        <v>-3.164338626851172</v>
+        <v>-3.164338626851161</v>
       </c>
       <c r="N41">
-        <v>0.3894157080433582</v>
+        <v>0.3894157080433471</v>
       </c>
     </row>
   </sheetData>
